--- a/data/trans_orig/IP07C13-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C13-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16734</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27200</t>
+          <t>26883</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14089</t>
+          <t>14527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33696</t>
+          <t>33661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47806</t>
+          <t>47361</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9495</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>17399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20315</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33539</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16527</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14709</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22902</t>
+          <t>23032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24904</t>
+          <t>25208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37080</t>
+          <t>37517</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14988</t>
+          <t>15158</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>14147</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15519</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27196</t>
+          <t>26846</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>519</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16823</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24001</t>
+          <t>23484</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35202</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34221</t>
+          <t>34855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48833</t>
+          <t>49294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>17897</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10985</t>
+          <t>11587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21616</t>
+          <t>22091</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23201</t>
+          <t>22919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37781</t>
+          <t>36751</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>708</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33198</t>
+          <t>32645</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47322</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41221</t>
+          <t>40956</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54832</t>
+          <t>55249</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>76899</t>
+          <t>77462</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97394</t>
+          <t>98327</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,96%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32066</t>
+          <t>31313</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45801</t>
+          <t>46614</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22733</t>
+          <t>22436</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36348</t>
+          <t>36752</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58945</t>
+          <t>58739</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>79986</t>
+          <t>78453</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23312</t>
+          <t>23586</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34218</t>
+          <t>34484</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27225</t>
+          <t>28161</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40223</t>
+          <t>40632</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>55330</t>
+          <t>55143</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>71003</t>
+          <t>72448</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>9556</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20758</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29758</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30469</t>
+          <t>30668</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46454</t>
+          <t>47772</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>43,45%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21909</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11786</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20616</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26292</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>39068</t>
+          <t>39042</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,01%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12620</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10451</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>26558</t>
+          <t>25781</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39541</t>
+          <t>38909</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>55,82%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>579</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>119828</t>
+          <t>118046</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>146445</t>
+          <t>144572</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>152323</t>
+          <t>152586</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>179432</t>
+          <t>179494</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>281202</t>
+          <t>280318</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>319129</t>
+          <t>317039</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,15%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>96864</t>
+          <t>97985</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>124012</t>
+          <t>124216</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>93528</t>
+          <t>93662</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>119564</t>
+          <t>120191</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>196500</t>
+          <t>199009</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>235004</t>
+          <t>234213</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26204</t>
+          <t>26243</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>21563</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>25235</t>
+          <t>25694</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>42568</t>
+          <t>44010</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>17933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27246</t>
+          <t>27496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18260</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27508</t>
+          <t>27029</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38626</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51961</t>
+          <t>51226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>15002</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>15012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27871</t>
+          <t>27411</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>26867</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>17405</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>26903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>37979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50317</t>
+          <t>50449</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15109</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13802</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26710</t>
+          <t>25713</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>37,98%</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25733</t>
+          <t>25395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>15594</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24005</t>
+          <t>24175</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33228</t>
+          <t>32364</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47733</t>
+          <t>47101</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,33%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24993</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23203</t>
+          <t>23603</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37191</t>
+          <t>37710</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45237</t>
+          <t>43711</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59730</t>
+          <t>59064</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55112</t>
+          <t>56104</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70577</t>
+          <t>70797</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>105103</t>
+          <t>105024</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>125606</t>
+          <t>126004</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16508</t>
+          <t>16288</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>29966</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>21780</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>35786</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40554</t>
+          <t>41659</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60464</t>
+          <t>61825</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7687</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>17055</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>32127</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45987</t>
+          <t>46376</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38133</t>
+          <t>37673</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51606</t>
+          <t>51241</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>73004</t>
+          <t>74835</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94014</t>
+          <t>94777</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21842</t>
+          <t>21222</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35108</t>
+          <t>35225</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17542</t>
+          <t>17758</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30616</t>
+          <t>31183</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42343</t>
+          <t>40793</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>61314</t>
+          <t>60508</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12596</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>575</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15405</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18593</t>
+          <t>18606</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15965</t>
+          <t>16493</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25688</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>30151</t>
+          <t>29698</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>41873</t>
+          <t>41686</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14148</t>
+          <t>14628</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>22278</t>
+          <t>22087</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>10554</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>156713</t>
+          <t>157024</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>184922</t>
+          <t>187166</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>180564</t>
+          <t>180509</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>208004</t>
+          <t>207343</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>343333</t>
+          <t>345398</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>384712</t>
+          <t>386052</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,37%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>82741</t>
+          <t>83549</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>109638</t>
+          <t>110882</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>80391</t>
+          <t>81522</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>106409</t>
+          <t>106553</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>171616</t>
+          <t>170487</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>209601</t>
+          <t>208420</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>28901</t>
+          <t>29826</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18363</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>25267</t>
+          <t>25212</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>43170</t>
+          <t>43505</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2016 (tasa de respuesta: 95,37%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2016 (tasa de respuesta: 95,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16823</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25545</t>
+          <t>25366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21151</t>
+          <t>20615</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30008</t>
+          <t>30172</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40225</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52752</t>
+          <t>53736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12705</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24644</t>
+          <t>24442</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19347</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30960</t>
+          <t>31123</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33183</t>
+          <t>33208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44330</t>
+          <t>45072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60821</t>
+          <t>61416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>63,33%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24393</t>
+          <t>23943</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24213</t>
+          <t>23652</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29139</t>
+          <t>28591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44617</t>
+          <t>43946</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19945</t>
+          <t>19879</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>25629</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29173</t>
+          <t>29265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42826</t>
+          <t>42530</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,63%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23428</t>
+          <t>23441</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21124</t>
+          <t>21580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35158</t>
+          <t>35036</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,42%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>630</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58266</t>
+          <t>58116</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75349</t>
+          <t>75490</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53003</t>
+          <t>53389</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69076</t>
+          <t>69318</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116598</t>
+          <t>115544</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138995</t>
+          <t>138459</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,5%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>26553</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43902</t>
+          <t>42955</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20914</t>
+          <t>21692</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37522</t>
+          <t>36452</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53215</t>
+          <t>53831</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>75537</t>
+          <t>74469</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13390</t>
+          <t>13787</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22222</t>
+          <t>21900</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31295</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>45299</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28936</t>
+          <t>29267</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43083</t>
+          <t>43431</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>65165</t>
+          <t>64994</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>85283</t>
+          <t>84700</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25057</t>
+          <t>25041</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38782</t>
+          <t>38662</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>18451</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31738</t>
+          <t>31567</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46280</t>
+          <t>46621</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>66615</t>
+          <t>66642</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15999</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>518</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20442</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>29864</t>
+          <t>29421</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>34989</t>
+          <t>34613</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>48638</t>
+          <t>48449</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,71%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>17466</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>16286</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29186</t>
+          <t>29463</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>168324</t>
+          <t>169607</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>197763</t>
+          <t>199482</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>182853</t>
+          <t>180736</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>212865</t>
+          <t>210407</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>360452</t>
+          <t>361406</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>402464</t>
+          <t>401744</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,16%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>101258</t>
+          <t>102285</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>129173</t>
+          <t>129947</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>94603</t>
+          <t>96142</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>122649</t>
+          <t>124446</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>205478</t>
+          <t>205760</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>245994</t>
+          <t>243559</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>15426</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>30524</t>
+          <t>29562</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>13451</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>26855</t>
+          <t>28106</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>31679</t>
+          <t>32217</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>51826</t>
+          <t>53207</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
